--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h3.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h3.xlsx
@@ -480,28 +480,28 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>1.076</v>
       </c>
       <c r="F2">
-        <v>0.9518</v>
+        <v>1.0322</v>
       </c>
       <c r="G2">
-        <v>-0.1242</v>
+        <v>-0.0437</v>
       </c>
       <c r="H2">
-        <v>-0.3198</v>
+        <v>0.3341</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K2">
         <v>18</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1.0466</v>
+        <v>1.1733</v>
       </c>
       <c r="F3">
-        <v>0.9055</v>
+        <v>0.9459</v>
       </c>
       <c r="G3">
-        <v>-0.1411</v>
+        <v>-0.2273</v>
       </c>
       <c r="H3">
-        <v>-0.3703</v>
+        <v>-0.654</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>1.1665</v>
+        <v>0.9223</v>
       </c>
       <c r="F4">
-        <v>1.0946</v>
+        <v>1.1685</v>
       </c>
       <c r="G4">
-        <v>-0.07190000000000001</v>
+        <v>0.2462</v>
       </c>
       <c r="H4">
-        <v>-0.1638</v>
+        <v>1.8943</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N4">
         <v>3</v>
